--- a/accountant_forms/014_ecommerce_bookkeeper_pre_screening_quiz--accountant_forms.xlsx
+++ b/accountant_forms/014_ecommerce_bookkeeper_pre_screening_quiz--accountant_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -707,7 +707,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C29"/>
+  <dimension ref="A1:C28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -905,17 +905,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>bookkeeper_qualification_choices</t>
+          <t>language_skills_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>certified_public_accountant</t>
+          <t>english</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Certified Public Accountant</t>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -927,12 +927,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>english</t>
+          <t>french</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>French</t>
         </is>
       </c>
     </row>
@@ -944,12 +944,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>french</t>
+          <t>spanish</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>French</t>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -961,12 +961,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>spanish</t>
+          <t>mandarin</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Spanish</t>
+          <t>Mandarin</t>
         </is>
       </c>
     </row>
@@ -978,29 +978,29 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>mandarin</t>
+          <t>arabic</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Mandarin</t>
+          <t>Arabic</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>language_skills_choices</t>
+          <t>bookkeeper_certification_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>arabic</t>
+          <t>cpa</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Arabic</t>
+          <t>CPA</t>
         </is>
       </c>
     </row>
@@ -1012,12 +1012,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>cpa</t>
+          <t>cpa_(australia)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>CPA</t>
+          <t>CPA (Australia)</t>
         </is>
       </c>
     </row>
@@ -1029,12 +1029,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>cpa_(australia)</t>
+          <t>cpa_(canada)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>CPA (Australia)</t>
+          <t>CPA (Canada)</t>
         </is>
       </c>
     </row>
@@ -1046,12 +1046,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>cpa_(canada)</t>
+          <t>cpa_(uk)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>CPA (Canada)</t>
+          <t>CPA (UK)</t>
         </is>
       </c>
     </row>
@@ -1063,12 +1063,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>cpa_(uk)</t>
+          <t>cpa_(us)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>CPA (UK)</t>
+          <t>CPA (US)</t>
         </is>
       </c>
     </row>
@@ -1080,29 +1080,29 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>cpa_(us)</t>
+          <t>cima</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>CPA (US)</t>
+          <t>CIMA</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>bookkeeper_certification_choices</t>
+          <t>availability_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>cima</t>
+          <t>full-time</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>CIMA</t>
+          <t>Full-time</t>
         </is>
       </c>
     </row>
@@ -1114,12 +1114,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>full-time</t>
+          <t>part-time</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Full-time</t>
+          <t>Part-time</t>
         </is>
       </c>
     </row>
@@ -1131,29 +1131,29 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>part-time</t>
+          <t>remote</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Part-time</t>
+          <t>Remote</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>availability_choices</t>
+          <t>work_type_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>remote</t>
+          <t>full-time</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Full-time</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>full-time</t>
+          <t>part-time</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Full-time</t>
+          <t>Part-time</t>
         </is>
       </c>
     </row>
@@ -1182,27 +1182,10 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>part-time</t>
+          <t>freelance</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
-        <is>
-          <t>Part-time</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>work_type_choices</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>freelance</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
         <is>
           <t>Freelance</t>
         </is>
